--- a/result/Table 1. Within_Across weighted mobility densities in Seoul (2020–2022).xlsx
+++ b/result/Table 1. Within_Across weighted mobility densities in Seoul (2020–2022).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/huzeyu/Desktop/UConnHealth/SeoulMobilityNetwork/result/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854095B0-C253-2040-94CA-1692CC0F81C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500FBECA-A7DA-9548-A6CD-08ADEBD95E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="700" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -643,12 +643,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -955,6 +954,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col min="4" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="14.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
@@ -989,7 +992,7 @@
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2">
         <v>667.46699999999998</v>
       </c>
       <c r="C2">
@@ -1018,7 +1021,7 @@
       <c r="A3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3">
         <v>580.101</v>
       </c>
       <c r="C3">
@@ -1047,7 +1050,7 @@
       <c r="A4" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4">
         <v>538.74199999999996</v>
       </c>
       <c r="C4">
@@ -1076,7 +1079,7 @@
       <c r="A5" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5">
         <v>516.66600000000005</v>
       </c>
       <c r="C5">
@@ -1105,7 +1108,7 @@
       <c r="A6" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6">
         <v>503.49099999999999</v>
       </c>
       <c r="C6">
@@ -1134,7 +1137,7 @@
       <c r="A7" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7">
         <v>477.27199999999999</v>
       </c>
       <c r="C7">
@@ -1163,7 +1166,7 @@
       <c r="A8" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8">
         <v>455.49</v>
       </c>
       <c r="C8">
@@ -1192,7 +1195,7 @@
       <c r="A9" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9">
         <v>450.76100000000002</v>
       </c>
       <c r="C9">
@@ -1221,7 +1224,7 @@
       <c r="A10" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10">
         <v>443.06</v>
       </c>
       <c r="C10">
@@ -1250,7 +1253,7 @@
       <c r="A11" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11">
         <v>417.88099999999997</v>
       </c>
       <c r="C11">
@@ -1279,7 +1282,7 @@
       <c r="A12" t="s">
         <v>79</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12">
         <v>407.548</v>
       </c>
       <c r="C12">
@@ -1308,7 +1311,7 @@
       <c r="A13" t="s">
         <v>86</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13">
         <v>402.12099999999998</v>
       </c>
       <c r="C13">
@@ -1337,7 +1340,7 @@
       <c r="A14" t="s">
         <v>93</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14">
         <v>395.45699999999999</v>
       </c>
       <c r="C14">
@@ -1366,7 +1369,7 @@
       <c r="A15" t="s">
         <v>100</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15">
         <v>393.86200000000002</v>
       </c>
       <c r="C15">
@@ -1395,7 +1398,7 @@
       <c r="A16" t="s">
         <v>107</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16">
         <v>378.71</v>
       </c>
       <c r="C16">
@@ -1424,7 +1427,7 @@
       <c r="A17" t="s">
         <v>114</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17">
         <v>354.66300000000001</v>
       </c>
       <c r="C17">
@@ -1453,7 +1456,7 @@
       <c r="A18" t="s">
         <v>121</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18">
         <v>354.20600000000002</v>
       </c>
       <c r="C18">
@@ -1482,7 +1485,7 @@
       <c r="A19" t="s">
         <v>128</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19">
         <v>320.24099999999999</v>
       </c>
       <c r="C19">
@@ -1511,7 +1514,7 @@
       <c r="A20" t="s">
         <v>135</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20">
         <v>319.38799999999998</v>
       </c>
       <c r="C20">
@@ -1540,7 +1543,7 @@
       <c r="A21" t="s">
         <v>142</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21">
         <v>303.94499999999999</v>
       </c>
       <c r="C21">
@@ -1569,7 +1572,7 @@
       <c r="A22" t="s">
         <v>149</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22">
         <v>293.80399999999997</v>
       </c>
       <c r="C22">
@@ -1598,7 +1601,7 @@
       <c r="A23" t="s">
         <v>156</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23">
         <v>245.18100000000001</v>
       </c>
       <c r="C23">
@@ -1627,7 +1630,7 @@
       <c r="A24" t="s">
         <v>163</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24">
         <v>238.405</v>
       </c>
       <c r="C24">
@@ -1656,7 +1659,7 @@
       <c r="A25" t="s">
         <v>170</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25">
         <v>154.999</v>
       </c>
       <c r="C25">
@@ -1685,7 +1688,7 @@
       <c r="A26" t="s">
         <v>177</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26">
         <v>132.40199999999999</v>
       </c>
       <c r="C26">
@@ -1714,7 +1717,7 @@
       <c r="A27" t="s">
         <v>184</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27">
         <v>9745.8629999999994</v>
       </c>
       <c r="C27">
